--- a/Profit_Calculator 1.0.1/output/Profit_Output.xlsx
+++ b/Profit_Calculator 1.0.1/output/Profit_Output.xlsx
@@ -260,7 +260,7 @@
     <tableColumn id="20" name="월 재료비(원)"/>
     <tableColumn id="21" name="월 인건비(원)"/>
     <tableColumn id="22" name="월 기기 대여비(원)"/>
-    <tableColumn id="23" name="감가상각 등 기타비(원)"/>
+    <tableColumn id="23" name="기타비용(원)"/>
     <tableColumn id="24" name="월 운영비(원)"/>
     <tableColumn id="25" name="월 영업이익(원)"/>
     <tableColumn id="26" name="공간 대여자 배분율"/>
@@ -292,8 +292,8 @@
     <tableColumn id="12" name="인건비 비율"/>
     <tableColumn id="13" name="기기 대여비(원)"/>
     <tableColumn id="14" name="기기 대여비 비율"/>
-    <tableColumn id="15" name="감가상각 등 기타비(원)"/>
-    <tableColumn id="16" name="기타비 비율"/>
+    <tableColumn id="15" name="기타비용(원)"/>
+    <tableColumn id="16" name="기타비용 비율"/>
     <tableColumn id="17" name="비용 비율 합계"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -338,8 +338,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ProfitInputGuide" displayName="ProfitInputGuide" ref="A3:D19" headerRowCount="1">
-  <autoFilter ref="A3:D19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ProfitInputGuide" displayName="ProfitInputGuide" ref="A3:D20" headerRowCount="1">
+  <autoFilter ref="A3:D20"/>
   <tableColumns count="4">
     <tableColumn id="1" name="구분"/>
     <tableColumn id="2" name="항목"/>
@@ -680,7 +680,7 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="21" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23 19:32:30</t>
+          <t>2026-08-23 19:58:48</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>감가상각 등 기타비(원)</t>
+          <t>기타비용(원)</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -954,25 +954,25 @@
         <v>2345200</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X5" s="6" t="n">
-        <v>17764147.60487051</v>
+        <v>17964147.60487051</v>
       </c>
       <c r="Y5" s="6" t="n">
-        <v>-8553907.604870513</v>
+        <v>-8753907.604870513</v>
       </c>
       <c r="Z5" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA5" s="6" t="n">
-        <v>-6843126.083896411</v>
+        <v>-7003126.083896411</v>
       </c>
       <c r="AB5" s="6" t="n">
-        <v>-8043126.083896411</v>
+        <v>-8203126.083896411</v>
       </c>
       <c r="AC5" s="6" t="n">
-        <v>-1710781.520974102</v>
+        <v>-1750781.520974102</v>
       </c>
       <c r="AD5" s="4" t="inlineStr">
         <is>
@@ -1061,25 +1061,25 @@
         <v>2345200</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X6" s="6" t="n">
-        <v>7596172.468267397</v>
+        <v>7796172.468267397</v>
       </c>
       <c r="Y6" s="6" t="n">
-        <v>3916627.531732605</v>
+        <v>3716627.531732605</v>
       </c>
       <c r="Z6" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA6" s="6" t="n">
-        <v>3133302.025386084</v>
+        <v>2973302.025386084</v>
       </c>
       <c r="AB6" s="6" t="n">
-        <v>1933302.025386084</v>
+        <v>1773302.025386084</v>
       </c>
       <c r="AC6" s="6" t="n">
-        <v>783325.506346521</v>
+        <v>743325.506346521</v>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
@@ -1168,25 +1168,25 @@
         <v>2345200</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X7" s="6" t="n">
-        <v>11425744.53315759</v>
+        <v>11625744.53315759</v>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>5843455.466842413</v>
+        <v>5643455.466842413</v>
       </c>
       <c r="Z7" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA7" s="6" t="n">
-        <v>4674764.37347393</v>
+        <v>4514764.37347393</v>
       </c>
       <c r="AB7" s="6" t="n">
-        <v>3474764.37347393</v>
+        <v>3314764.37347393</v>
       </c>
       <c r="AC7" s="6" t="n">
-        <v>1168691.093368483</v>
+        <v>1128691.093368483</v>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
@@ -1275,25 +1275,25 @@
         <v>2345200</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X8" s="6" t="n">
-        <v>10802412.22942977</v>
+        <v>11002412.22942977</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <v>20512403.77057023</v>
+        <v>20312403.77057023</v>
       </c>
       <c r="Z8" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA8" s="6" t="n">
-        <v>16409923.01645618</v>
+        <v>16249923.01645618</v>
       </c>
       <c r="AB8" s="6" t="n">
-        <v>15209923.01645618</v>
+        <v>15049923.01645618</v>
       </c>
       <c r="AC8" s="6" t="n">
-        <v>4102480.754114045</v>
+        <v>4062480.754114045</v>
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
@@ -1382,25 +1382,25 @@
         <v>2345200</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X9" s="6" t="n">
-        <v>10827203.90133637</v>
+        <v>11027203.90133637</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>-5070803.901336366</v>
+        <v>-5270803.901336366</v>
       </c>
       <c r="Z9" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA9" s="6" t="n">
-        <v>-4056643.121069093</v>
+        <v>-4216643.121069093</v>
       </c>
       <c r="AB9" s="6" t="n">
-        <v>-5256643.121069093</v>
+        <v>-5416643.121069093</v>
       </c>
       <c r="AC9" s="6" t="n">
-        <v>-1014160.780267273</v>
+        <v>-1054160.780267273</v>
       </c>
       <c r="AD9" s="4" t="inlineStr">
         <is>
@@ -1489,25 +1489,25 @@
         <v>2345200</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X10" s="6" t="n">
-        <v>10669610.27195958</v>
+        <v>10869610.27195958</v>
       </c>
       <c r="Y10" s="6" t="n">
-        <v>843189.7280404214</v>
+        <v>643189.7280404214</v>
       </c>
       <c r="Z10" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA10" s="6" t="n">
-        <v>674551.7824323372</v>
+        <v>514551.7824323371</v>
       </c>
       <c r="AB10" s="6" t="n">
-        <v>-525448.2175676628</v>
+        <v>-685448.2175676629</v>
       </c>
       <c r="AC10" s="6" t="n">
-        <v>168637.9456080842</v>
+        <v>128637.9456080843</v>
       </c>
       <c r="AD10" s="4" t="inlineStr">
         <is>
@@ -1596,25 +1596,25 @@
         <v>943800</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X11" s="6" t="n">
-        <v>7209647.382836675</v>
+        <v>7409647.382836675</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>-3503087.382836675</v>
+        <v>-3703087.382836675</v>
       </c>
       <c r="Z11" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>-2802469.90626934</v>
+        <v>-2962469.90626934</v>
       </c>
       <c r="AB11" s="6" t="n">
-        <v>-3602469.90626934</v>
+        <v>-3762469.90626934</v>
       </c>
       <c r="AC11" s="6" t="n">
-        <v>-700617.476567335</v>
+        <v>-740617.476567335</v>
       </c>
       <c r="AD11" s="4" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
         <v>943800</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X12" s="6" t="n">
-        <v>3117422.547631619</v>
+        <v>3317422.547631619</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>1515777.452368381</v>
+        <v>1315777.452368381</v>
       </c>
       <c r="Z12" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA12" s="6" t="n">
-        <v>1212621.961894705</v>
+        <v>1052621.961894705</v>
       </c>
       <c r="AB12" s="6" t="n">
-        <v>412621.9618947052</v>
+        <v>252621.9618947052</v>
       </c>
       <c r="AC12" s="6" t="n">
-        <v>303155.4904736762</v>
+        <v>263155.4904736762</v>
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
@@ -1810,25 +1810,25 @@
         <v>943800</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X13" s="6" t="n">
-        <v>4658539.832500195</v>
+        <v>4858539.832500195</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>2291260.167499806</v>
+        <v>2091260.167499806</v>
       </c>
       <c r="Z13" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA13" s="6" t="n">
-        <v>1833008.133999845</v>
+        <v>1673008.133999845</v>
       </c>
       <c r="AB13" s="6" t="n">
-        <v>1033008.133999845</v>
+        <v>873008.1339998448</v>
       </c>
       <c r="AC13" s="6" t="n">
-        <v>458252.033499961</v>
+        <v>418252.033499961</v>
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
@@ -1917,25 +1917,25 @@
         <v>943800</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X14" s="6" t="n">
-        <v>4408775.284457612</v>
+        <v>4608775.284457612</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>8193528.715542388</v>
+        <v>7993528.715542388</v>
       </c>
       <c r="Z14" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA14" s="6" t="n">
-        <v>6554822.972433911</v>
+        <v>6394822.972433911</v>
       </c>
       <c r="AB14" s="6" t="n">
-        <v>5754822.972433911</v>
+        <v>5594822.972433911</v>
       </c>
       <c r="AC14" s="6" t="n">
-        <v>1638705.743108477</v>
+        <v>1598705.743108477</v>
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
@@ -2024,25 +2024,25 @@
         <v>943800</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X15" s="6" t="n">
-        <v>4417715.685330106</v>
+        <v>4617715.685330106</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>-2101115.685330106</v>
+        <v>-2301115.685330106</v>
       </c>
       <c r="Z15" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA15" s="6" t="n">
-        <v>-1680892.548264085</v>
+        <v>-1840892.548264085</v>
       </c>
       <c r="AB15" s="6" t="n">
-        <v>-2480892.548264085</v>
+        <v>-2640892.548264085</v>
       </c>
       <c r="AC15" s="6" t="n">
-        <v>-420223.1370660211</v>
+        <v>-460223.1370660211</v>
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
@@ -2131,25 +2131,25 @@
         <v>943800</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X16" s="6" t="n">
-        <v>4355513.361616092</v>
+        <v>4555513.361616092</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>277686.6383839082</v>
+        <v>77686.6383839082</v>
       </c>
       <c r="Z16" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA16" s="6" t="n">
-        <v>222149.3107071266</v>
+        <v>62149.31070712656</v>
       </c>
       <c r="AB16" s="6" t="n">
-        <v>-577850.6892928735</v>
+        <v>-737850.6892928735</v>
       </c>
       <c r="AC16" s="6" t="n">
-        <v>55537.32767678163</v>
+        <v>15537.32767678164</v>
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
@@ -2238,25 +2238,25 @@
         <v>4633200</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X17" s="6" t="n">
-        <v>34995237.98005187</v>
+        <v>35195237.98005187</v>
       </c>
       <c r="Y17" s="6" t="n">
-        <v>-16799397.98005187</v>
+        <v>-16999397.98005187</v>
       </c>
       <c r="Z17" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA17" s="6" t="n">
-        <v>-13439518.3840415</v>
+        <v>-13599518.3840415</v>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>-16939518.3840415</v>
+        <v>-17099518.3840415</v>
       </c>
       <c r="AC17" s="6" t="n">
-        <v>-3359879.596010372</v>
+        <v>-3399879.596010372</v>
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
@@ -2345,25 +2345,25 @@
         <v>4633200</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X18" s="6" t="n">
-        <v>14907864.27223456</v>
+        <v>15107864.27223456</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>7836935.727765441</v>
+        <v>7636935.727765441</v>
       </c>
       <c r="Z18" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA18" s="6" t="n">
-        <v>6269548.582212353</v>
+        <v>6109548.582212353</v>
       </c>
       <c r="AB18" s="6" t="n">
-        <v>2769548.582212353</v>
+        <v>2609548.582212353</v>
       </c>
       <c r="AC18" s="6" t="n">
-        <v>1567387.145553088</v>
+        <v>1527387.145553088</v>
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
@@ -2452,25 +2452,25 @@
         <v>4633200</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X19" s="6" t="n">
-        <v>22473731.90983614</v>
+        <v>22673731.90983614</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>11643468.09016386</v>
+        <v>11443468.09016386</v>
       </c>
       <c r="Z19" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA19" s="6" t="n">
-        <v>9314774.472131087</v>
+        <v>9154774.472131087</v>
       </c>
       <c r="AB19" s="6" t="n">
-        <v>5814774.472131087</v>
+        <v>5654774.472131087</v>
       </c>
       <c r="AC19" s="6" t="n">
-        <v>2328693.61803277</v>
+        <v>2288693.61803277</v>
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
@@ -2559,25 +2559,25 @@
         <v>4633200</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X20" s="6" t="n">
-        <v>21239594.82883243</v>
+        <v>21439594.82883243</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>40626261.17116757</v>
+        <v>40426261.17116757</v>
       </c>
       <c r="Z20" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA20" s="6" t="n">
-        <v>32501008.93693405</v>
+        <v>32341008.93693405</v>
       </c>
       <c r="AB20" s="6" t="n">
-        <v>29001008.93693405</v>
+        <v>28841008.93693405</v>
       </c>
       <c r="AC20" s="6" t="n">
-        <v>8125252.234233513</v>
+        <v>8085252.234233513</v>
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
@@ -2666,25 +2666,25 @@
         <v>4633200</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X21" s="6" t="n">
-        <v>21291121.4936635</v>
+        <v>21491121.4936635</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>-9918721.493663497</v>
+        <v>-10118721.4936635</v>
       </c>
       <c r="Z21" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA21" s="6" t="n">
-        <v>-7934977.194930798</v>
+        <v>-8094977.194930798</v>
       </c>
       <c r="AB21" s="6" t="n">
-        <v>-11434977.1949308</v>
+        <v>-11594977.1949308</v>
       </c>
       <c r="AC21" s="6" t="n">
-        <v>-1983744.298732699</v>
+        <v>-2023744.298732699</v>
       </c>
       <c r="AD21" s="4" t="inlineStr">
         <is>
@@ -2773,25 +2773,25 @@
         <v>4633200</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="X22" s="6" t="n">
-        <v>20976780.79667662</v>
+        <v>21176780.79667662</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>1768019.203323379</v>
+        <v>1568019.203323379</v>
       </c>
       <c r="Z22" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="AA22" s="6" t="n">
-        <v>1414415.362658703</v>
+        <v>1254415.362658703</v>
       </c>
       <c r="AB22" s="6" t="n">
-        <v>-2085584.637341297</v>
+        <v>-2245584.637341296</v>
       </c>
       <c r="AC22" s="6" t="n">
-        <v>353603.8406646757</v>
+        <v>313603.8406646757</v>
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>감가상각 등 기타비(원)</t>
+          <t>기타비용(원)</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>기타비 비율</t>
+          <t>기타비용 비율</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>17764147.60487051</v>
+        <v>17964147.60487051</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>5547057.390584799</v>
@@ -3044,7 +3044,7 @@
         <v/>
       </c>
       <c r="O5" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P5" s="9">
         <f>IF($D5=0,0,O5/$D5)</f>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>7596172.468267397</v>
+        <v>7796172.468267397</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>2003136.456362635</v>
@@ -3110,7 +3110,7 @@
         <v/>
       </c>
       <c r="O6" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P6" s="9">
         <f>IF($D6=0,0,O6/$D6)</f>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>11425744.53315759</v>
+        <v>11625744.53315759</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>3151514.83910997</v>
@@ -3176,7 +3176,7 @@
         <v/>
       </c>
       <c r="O7" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P7" s="9">
         <f>IF($D7=0,0,O7/$D7)</f>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>10802412.22942977</v>
+        <v>11002412.22942977</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>3796927.994191677</v>
@@ -3242,7 +3242,7 @@
         <v/>
       </c>
       <c r="O8" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P8" s="9">
         <f>IF($D8=0,0,O8/$D8)</f>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>10827203.90133637</v>
+        <v>11027203.90133637</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>4126426.37514589</v>
@@ -3308,7 +3308,7 @@
         <v/>
       </c>
       <c r="O9" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P9" s="9">
         <f>IF($D9=0,0,O9/$D9)</f>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>10669610.27195958</v>
+        <v>10869610.27195958</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>3659691.679769103</v>
@@ -3374,7 +3374,7 @@
         <v/>
       </c>
       <c r="O10" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P10" s="9">
         <f>IF($D10=0,0,O10/$D10)</f>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>7209647.382836675</v>
+        <v>7409647.382836675</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>2233257.418550962</v>
@@ -3440,7 +3440,7 @@
         <v/>
       </c>
       <c r="O11" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P11" s="9">
         <f>IF($D11=0,0,O11/$D11)</f>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3117422.547631619</v>
+        <v>3317422.547631619</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>806810.4940601898</v>
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="O12" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P12" s="9">
         <f>IF($D12=0,0,O12/$D12)</f>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>4658539.832500195</v>
+        <v>4858539.832500195</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>1268910.809285909</v>
@@ -3572,7 +3572,7 @@
         <v/>
       </c>
       <c r="O13" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P13" s="9">
         <f>IF($D13=0,0,O13/$D13)</f>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4408775.284457612</v>
+        <v>4608775.284457612</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>1529738.945886183</v>
@@ -3638,7 +3638,7 @@
         <v/>
       </c>
       <c r="O14" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P14" s="9">
         <f>IF($D14=0,0,O14/$D14)</f>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>4417715.685330106</v>
+        <v>4617715.685330106</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>1661305.217472963</v>
@@ -3704,7 +3704,7 @@
         <v/>
       </c>
       <c r="O15" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P15" s="9">
         <f>IF($D15=0,0,O15/$D15)</f>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>4355513.361616092</v>
+        <v>4555513.361616092</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1474692.464758949</v>
@@ -3770,7 +3770,7 @@
         <v/>
       </c>
       <c r="O16" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P16" s="9">
         <f>IF($D16=0,0,O16/$D16)</f>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>34995237.98005187</v>
+        <v>35195237.98005187</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>10956596.33719473</v>
@@ -3836,7 +3836,7 @@
         <v/>
       </c>
       <c r="O17" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P17" s="9">
         <f>IF($D17=0,0,O17/$D17)</f>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>14907864.27223456</v>
+        <v>15107864.27223456</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>3955768.736520273</v>
@@ -3902,7 +3902,7 @@
         <v/>
       </c>
       <c r="O18" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P18" s="9">
         <f>IF($D18=0,0,O18/$D18)</f>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22473731.90983614</v>
+        <v>22673731.90983614</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>6224643.977693288</v>
@@ -3968,7 +3968,7 @@
         <v/>
       </c>
       <c r="O19" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P19" s="9">
         <f>IF($D19=0,0,O19/$D19)</f>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>21239594.82883243</v>
+        <v>21439594.82883243</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>7497052.803118148</v>
@@ -4034,7 +4034,7 @@
         <v/>
       </c>
       <c r="O20" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P20" s="9">
         <f>IF($D20=0,0,O20/$D20)</f>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>21291121.4936635</v>
+        <v>21491121.4936635</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>8150561.015092068</v>
@@ -4100,7 +4100,7 @@
         <v/>
       </c>
       <c r="O21" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P21" s="9">
         <f>IF($D21=0,0,O21/$D21)</f>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>20976780.79667662</v>
+        <v>21176780.79667662</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>7225478.212105193</v>
@@ -4166,7 +4166,7 @@
         <v/>
       </c>
       <c r="O22" s="8" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="P22" s="9">
         <f>IF($D22=0,0,O22/$D22)</f>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>17764147.60487051</v>
+        <v>17964147.60487051</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-8553907.604870513</v>
+        <v>-8753907.604870513</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-6843126.083896411</v>
+        <v>-7003126.083896411</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-8043126.083896411</v>
+        <v>-8203126.083896411</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-1710781.520974102</v>
+        <v>-1750781.520974102</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         </is>
       </c>
       <c r="F70" s="8" t="n">
-        <v>7596172.468267397</v>
+        <v>7796172.468267397</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="F71" s="8" t="n">
-        <v>3916627.531732605</v>
+        <v>3716627.531732605</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>3133302.025386084</v>
+        <v>2973302.025386084</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>1933302.025386084</v>
+        <v>1773302.025386084</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="F75" s="8" t="n">
-        <v>783325.506346521</v>
+        <v>743325.506346521</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>11425744.53315759</v>
+        <v>11625744.53315759</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="F107" s="8" t="n">
-        <v>5843455.466842413</v>
+        <v>5643455.466842413</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="F108" s="8" t="n">
-        <v>4674764.37347393</v>
+        <v>4514764.37347393</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="F110" s="8" t="n">
-        <v>3474764.37347393</v>
+        <v>3314764.37347393</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="F111" s="8" t="n">
-        <v>1168691.093368483</v>
+        <v>1128691.093368483</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="F142" s="8" t="n">
-        <v>10802412.22942977</v>
+        <v>11002412.22942977</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="F143" s="8" t="n">
-        <v>20512403.77057023</v>
+        <v>20312403.77057023</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="F144" s="8" t="n">
-        <v>16409923.01645618</v>
+        <v>16249923.01645618</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="F146" s="8" t="n">
-        <v>15209923.01645618</v>
+        <v>15049923.01645618</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="F147" s="8" t="n">
-        <v>4102480.754114045</v>
+        <v>4062480.754114045</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         </is>
       </c>
       <c r="F178" s="8" t="n">
-        <v>10827203.90133637</v>
+        <v>11027203.90133637</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="F179" s="8" t="n">
-        <v>-5070803.901336366</v>
+        <v>-5270803.901336366</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         </is>
       </c>
       <c r="F180" s="8" t="n">
-        <v>-4056643.121069093</v>
+        <v>-4216643.121069093</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="F182" s="8" t="n">
-        <v>-5256643.121069093</v>
+        <v>-5416643.121069093</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="F183" s="8" t="n">
-        <v>-1014160.780267273</v>
+        <v>-1054160.780267273</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="F214" s="8" t="n">
-        <v>10669610.27195958</v>
+        <v>10869610.27195958</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="F215" s="8" t="n">
-        <v>843189.7280404214</v>
+        <v>643189.7280404214</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="F216" s="8" t="n">
-        <v>674551.7824323372</v>
+        <v>514551.7824323371</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="F218" s="8" t="n">
-        <v>-525448.2175676628</v>
+        <v>-685448.2175676629</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         </is>
       </c>
       <c r="F219" s="8" t="n">
-        <v>168637.9456080842</v>
+        <v>128637.9456080843</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         </is>
       </c>
       <c r="F250" s="8" t="n">
-        <v>7209647.382836675</v>
+        <v>7409647.382836675</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="F251" s="8" t="n">
-        <v>-3503087.382836675</v>
+        <v>-3703087.382836675</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         </is>
       </c>
       <c r="F252" s="8" t="n">
-        <v>-2802469.90626934</v>
+        <v>-2962469.90626934</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="F254" s="8" t="n">
-        <v>-3602469.90626934</v>
+        <v>-3762469.90626934</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         </is>
       </c>
       <c r="F255" s="8" t="n">
-        <v>-700617.476567335</v>
+        <v>-740617.476567335</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="F286" s="8" t="n">
-        <v>3117422.547631619</v>
+        <v>3317422.547631619</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         </is>
       </c>
       <c r="F287" s="8" t="n">
-        <v>1515777.452368381</v>
+        <v>1315777.452368381</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="F288" s="8" t="n">
-        <v>1212621.961894705</v>
+        <v>1052621.961894705</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         </is>
       </c>
       <c r="F290" s="8" t="n">
-        <v>412621.9618947052</v>
+        <v>252621.9618947052</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="F291" s="8" t="n">
-        <v>303155.4904736762</v>
+        <v>263155.4904736762</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         </is>
       </c>
       <c r="F322" s="8" t="n">
-        <v>4658539.832500195</v>
+        <v>4858539.832500195</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         </is>
       </c>
       <c r="F323" s="8" t="n">
-        <v>2291260.167499806</v>
+        <v>2091260.167499806</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="F324" s="8" t="n">
-        <v>1833008.133999845</v>
+        <v>1673008.133999845</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="F326" s="8" t="n">
-        <v>1033008.133999845</v>
+        <v>873008.1339998448</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         </is>
       </c>
       <c r="F327" s="8" t="n">
-        <v>458252.033499961</v>
+        <v>418252.033499961</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="F358" s="8" t="n">
-        <v>4408775.284457612</v>
+        <v>4608775.284457612</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         </is>
       </c>
       <c r="F359" s="8" t="n">
-        <v>8193528.715542388</v>
+        <v>7993528.715542388</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         </is>
       </c>
       <c r="F360" s="8" t="n">
-        <v>6554822.972433911</v>
+        <v>6394822.972433911</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         </is>
       </c>
       <c r="F362" s="8" t="n">
-        <v>5754822.972433911</v>
+        <v>5594822.972433911</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         </is>
       </c>
       <c r="F363" s="8" t="n">
-        <v>1638705.743108477</v>
+        <v>1598705.743108477</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="F394" s="8" t="n">
-        <v>4417715.685330106</v>
+        <v>4617715.685330106</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         </is>
       </c>
       <c r="F395" s="8" t="n">
-        <v>-2101115.685330106</v>
+        <v>-2301115.685330106</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="F396" s="8" t="n">
-        <v>-1680892.548264085</v>
+        <v>-1840892.548264085</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="F398" s="8" t="n">
-        <v>-2480892.548264085</v>
+        <v>-2640892.548264085</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="F399" s="8" t="n">
-        <v>-420223.1370660211</v>
+        <v>-460223.1370660211</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         </is>
       </c>
       <c r="F430" s="8" t="n">
-        <v>4355513.361616092</v>
+        <v>4555513.361616092</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="F431" s="8" t="n">
-        <v>277686.6383839082</v>
+        <v>77686.6383839082</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         </is>
       </c>
       <c r="F432" s="8" t="n">
-        <v>222149.3107071266</v>
+        <v>62149.31070712656</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         </is>
       </c>
       <c r="F434" s="8" t="n">
-        <v>-577850.6892928735</v>
+        <v>-737850.6892928735</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         </is>
       </c>
       <c r="F435" s="8" t="n">
-        <v>55537.32767678163</v>
+        <v>15537.32767678164</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="F466" s="8" t="n">
-        <v>34995237.98005187</v>
+        <v>35195237.98005187</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         </is>
       </c>
       <c r="F467" s="8" t="n">
-        <v>-16799397.98005187</v>
+        <v>-16999397.98005187</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         </is>
       </c>
       <c r="F468" s="8" t="n">
-        <v>-13439518.3840415</v>
+        <v>-13599518.3840415</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         </is>
       </c>
       <c r="F470" s="8" t="n">
-        <v>-16939518.3840415</v>
+        <v>-17099518.3840415</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="F471" s="8" t="n">
-        <v>-3359879.596010372</v>
+        <v>-3399879.596010372</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         </is>
       </c>
       <c r="F502" s="8" t="n">
-        <v>14907864.27223456</v>
+        <v>15107864.27223456</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         </is>
       </c>
       <c r="F503" s="8" t="n">
-        <v>7836935.727765441</v>
+        <v>7636935.727765441</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         </is>
       </c>
       <c r="F504" s="8" t="n">
-        <v>6269548.582212353</v>
+        <v>6109548.582212353</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         </is>
       </c>
       <c r="F506" s="8" t="n">
-        <v>2769548.582212353</v>
+        <v>2609548.582212353</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         </is>
       </c>
       <c r="F507" s="8" t="n">
-        <v>1567387.145553088</v>
+        <v>1527387.145553088</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         </is>
       </c>
       <c r="F538" s="8" t="n">
-        <v>22473731.90983614</v>
+        <v>22673731.90983614</v>
       </c>
       <c r="G538" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         </is>
       </c>
       <c r="F539" s="8" t="n">
-        <v>11643468.09016386</v>
+        <v>11443468.09016386</v>
       </c>
       <c r="G539" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         </is>
       </c>
       <c r="F540" s="8" t="n">
-        <v>9314774.472131087</v>
+        <v>9154774.472131087</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         </is>
       </c>
       <c r="F542" s="8" t="n">
-        <v>5814774.472131087</v>
+        <v>5654774.472131087</v>
       </c>
       <c r="G542" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         </is>
       </c>
       <c r="F543" s="8" t="n">
-        <v>2328693.61803277</v>
+        <v>2288693.61803277</v>
       </c>
       <c r="G543" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         </is>
       </c>
       <c r="F574" s="8" t="n">
-        <v>21239594.82883243</v>
+        <v>21439594.82883243</v>
       </c>
       <c r="G574" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="F575" s="8" t="n">
-        <v>40626261.17116757</v>
+        <v>40426261.17116757</v>
       </c>
       <c r="G575" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         </is>
       </c>
       <c r="F576" s="8" t="n">
-        <v>32501008.93693405</v>
+        <v>32341008.93693405</v>
       </c>
       <c r="G576" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         </is>
       </c>
       <c r="F578" s="8" t="n">
-        <v>29001008.93693405</v>
+        <v>28841008.93693405</v>
       </c>
       <c r="G578" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         </is>
       </c>
       <c r="F579" s="8" t="n">
-        <v>8125252.234233513</v>
+        <v>8085252.234233513</v>
       </c>
       <c r="G579" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         </is>
       </c>
       <c r="F610" s="8" t="n">
-        <v>21291121.4936635</v>
+        <v>21491121.4936635</v>
       </c>
       <c r="G610" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         </is>
       </c>
       <c r="F611" s="8" t="n">
-        <v>-9918721.493663497</v>
+        <v>-10118721.4936635</v>
       </c>
       <c r="G611" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         </is>
       </c>
       <c r="F612" s="8" t="n">
-        <v>-7934977.194930798</v>
+        <v>-8094977.194930798</v>
       </c>
       <c r="G612" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         </is>
       </c>
       <c r="F614" s="8" t="n">
-        <v>-11434977.1949308</v>
+        <v>-11594977.1949308</v>
       </c>
       <c r="G614" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         </is>
       </c>
       <c r="F615" s="8" t="n">
-        <v>-1983744.298732699</v>
+        <v>-2023744.298732699</v>
       </c>
       <c r="G615" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         </is>
       </c>
       <c r="F646" s="8" t="n">
-        <v>20976780.79667662</v>
+        <v>21176780.79667662</v>
       </c>
       <c r="G646" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         </is>
       </c>
       <c r="F647" s="8" t="n">
-        <v>1768019.203323379</v>
+        <v>1568019.203323379</v>
       </c>
       <c r="G647" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         </is>
       </c>
       <c r="F648" s="8" t="n">
-        <v>1414415.362658703</v>
+        <v>1254415.362658703</v>
       </c>
       <c r="G648" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         </is>
       </c>
       <c r="F650" s="8" t="n">
-        <v>-2085584.637341297</v>
+        <v>-2245584.637341296</v>
       </c>
       <c r="G650" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="F651" s="8" t="n">
-        <v>353603.8406646757</v>
+        <v>313603.8406646757</v>
       </c>
       <c r="G651" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -37123,22 +37123,22 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>수도</t>
+          <t>비용</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>배액률</t>
+          <t>월 기타비용</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>300,000 원/month</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>standard_info.csv 공통값; 모든 작물에 동일 적용</t>
+          <t>standard_info.csv 공통값; 모든 시나리오에 월 1회 적용</t>
         </is>
       </c>
     </row>
@@ -37150,61 +37150,61 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>수도 종합단가</t>
+          <t>배액률</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>2,300 원/m³</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>standard_info.csv 입력</t>
+          <t>standard_info.csv 공통값; 모든 작물에 동일 적용</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>수익</t>
+          <t>수도</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>공간 대여자 배분비율</t>
+          <t>수도 종합단가</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2,300 원/m³</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>contraction_info.csv 입력</t>
+          <t>standard_info.csv 입력</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>재료비</t>
+          <t>수익</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>모종비 적용 기준</t>
+          <t>공간 대여자 배분비율</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>기존 1회 단가의 1/3을 매월 적용</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>기존 단가로 연 4회 구입하는 것과 같은 연간 비용</t>
+          <t>contraction_info.csv 입력</t>
         </is>
       </c>
     </row>
@@ -37216,39 +37216,39 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>양액 단가</t>
+          <t>모종비 적용 기준</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>20 원/L</t>
+          <t>기존 1회 단가의 1/3을 매월 적용</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>standard_info.csv 입력; 순환식 손실·보충 보정계수 1.1 적용</t>
+          <t>기존 단가로 연 4회 구입하는 것과 같은 연간 비용</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>추천</t>
+          <t>재료비</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>장기계약형</t>
+          <t>양액 단가</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>예상수익 ≥ 원하는 월세</t>
+          <t>20 원/L</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>두 금액이 같아도 장기계약형</t>
+          <t>standard_info.csv 입력; 순환식 손실·보충 보정계수 1.1 적용</t>
         </is>
       </c>
     </row>
@@ -37260,39 +37260,39 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>단기계약형</t>
+          <t>장기계약형</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>적자 또는 예상수익 &lt; 원하는 월세</t>
+          <t>예상수익 ≥ 원하는 월세</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>적자 금액은 그대로 출력</t>
+          <t>두 금액이 같아도 장기계약형</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>입력 파일</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>공간정보</t>
+          <t>단기계약형</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>data/space_info.csv</t>
+          <t>적자 또는 예상수익 &lt; 원하는 월세</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>사업장별 원하는 월세 포함</t>
+          <t>적자 금액은 그대로 출력</t>
         </is>
       </c>
     </row>
@@ -37304,81 +37304,103 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>작물 생산정보</t>
+          <t>공간정보</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>data/crop_production_info.csv</t>
+          <t>data/space_info.csv</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>상추·딸기·바질·애플민트·쪽파·병풀 및 작물별 모듈 층 수</t>
+          <t>사업장별 원하는 월세 포함</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>작물</t>
+          <t>입력 파일</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>작물별 모듈 층 수</t>
+          <t>작물 생산정보</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>상추 4층 · 딸기 2층 · 바질 3층 · 애플민트 4층 · 쪽파 3층 · 병풀 3층</t>
+          <t>data/crop_production_info.csv</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>crop_production_info.csv 입력</t>
+          <t>상추·딸기·바질·애플민트·쪽파·병풀 및 작물별 모듈 층 수</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>입력 파일</t>
+          <t>작물</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>작물 판매정보</t>
+          <t>작물별 모듈 층 수</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>data/crop_sale_info.csv</t>
+          <t>상추 4층 · 딸기 2층 · 바질 3층 · 애플민트 4층 · 쪽파 3층 · 병풀 3층</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>작물별 kg당 판매가격</t>
+          <t>crop_production_info.csv 입력</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>입력 파일</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>작물 판매정보</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>data/crop_sale_info.csv</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>작물별 kg당 판매가격</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
           <t>주의</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>18개 결과 합산</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>비교용</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>같은 공간의 대안 작물을 동시에 운영한 합계가 아님</t>
         </is>
@@ -37539,7 +37561,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C7" s="8">
@@ -37632,7 +37654,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C10" s="8">
@@ -37725,7 +37747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C13" s="8">
@@ -37818,7 +37840,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C16" s="8">
@@ -37911,7 +37933,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C19" s="8">
@@ -38004,7 +38026,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C22" s="8">
@@ -38097,7 +38119,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C25" s="8">
@@ -38190,7 +38212,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C28" s="8">
@@ -38283,7 +38305,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C31" s="8">
@@ -38376,7 +38398,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C34" s="8">
@@ -38469,7 +38491,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C37" s="8">
@@ -38562,7 +38584,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C40" s="8">
@@ -38655,7 +38677,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C43" s="8">
@@ -38748,7 +38770,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C46" s="8">
@@ -38841,7 +38863,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C49" s="8">
@@ -38934,7 +38956,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C52" s="8">
@@ -39027,7 +39049,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C55" s="8">
@@ -39120,7 +39142,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비</t>
+          <t>월 운영비 = 전기비 + 수도비 + 재료비 + 인건비 + 기기 대여비 + 기타비용</t>
         </is>
       </c>
       <c r="C58" s="8">
